--- a/data/trans_camb/IP16B05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Estudios-trans_camb.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,84</t>
+          <t>0,0; 38,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,59</t>
+          <t>0,0; 40,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 0,0</t>
+          <t>-26,64; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 15,81</t>
+          <t>-4,49; 15,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,7</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,93</t>
+          <t>0,0; 62,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,2</t>
+          <t>0,0; 67,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 0,0</t>
+          <t>-26,64; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 18,66</t>
+          <t>-4,49; 18,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,53</t>
+          <t>0,0; 23,91</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 24,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,44</t>
+          <t>0,0; 28,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,95</t>
+          <t>-2,25; 10,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 10,81</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 31,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 40,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 0,0</t>
+          <t>-15,28; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,04</t>
+          <t>-2,25; 11,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,34</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B05-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Estudios-trans_camb.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,14</t>
+          <t>0,0; 33,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,2</t>
+          <t>0,0; 33,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 0,0</t>
+          <t>-23,32; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 15,79</t>
+          <t>-4,58; 13,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 19,52</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,17</t>
+          <t>0,0; 50,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,23</t>
+          <t>0,0; 50,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 0,0</t>
+          <t>-23,32; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 18,64</t>
+          <t>-4,58; 16,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,91</t>
+          <t>0,0; 24,26</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,09</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,67</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,6</t>
+          <t>-2,93; 9,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,81</t>
+          <t>0,0; 13,66</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,74</t>
+          <t>0,0; 34,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,29</t>
+          <t>0,0; 43,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 0,0</t>
+          <t>-14,03; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,94</t>
+          <t>-2,93; 10,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 15,84</t>
         </is>
       </c>
     </row>
